--- a/appiumtest/Android_Appium_Test_Results.xlsx
+++ b/appiumtest/Android_Appium_Test_Results.xlsx
@@ -515,7 +515,6 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
